--- a/results/job_matches_2026-08-03.xlsx
+++ b/results/job_matches_2026-08-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=75d032017053c612</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QA &amp; Operations Engineer – Amazon Connect (CCaaS)</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e45a080aab120d</t>
+          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Backend Software Engineer Intern (TikTok- PGC-Digital Content Center) - 2027 Summer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rocklin, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, MapReduce, Spark, Scala, ETL, Talend, Python, SQL</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e235cc7e99c3a2a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior AWS / Amazon Connect Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=adf03900850392a3</t>
+          <t>https://www.indeed.com/viewjob?jk=df7f3bd6cb74fbdd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-03.xlsx
+++ b/results/job_matches_2026-08-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,235 +468,235 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, DBT, ETL)</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1c4c6a8a8c46e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec018f4b793bb53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, DBT, ETL)</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e11531ce39be3674</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5406e0a898c0b3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, DBT, ETL)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82f7de5f84e4fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=51afe960d8622afb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Java Developer with E-Trading exp must</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NSV IT SOLUTIONS</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>21.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b93bfb157e46dad0</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bdbda24615b096</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>21.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d032017053c612</t>
+          <t>https://www.indeed.com/viewjob?jk=8a792597231fd045</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>21.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=49b79f56ab220c49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Senior Software Engineer (Python, DBT, ETL)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd1c4c6a8a8c46e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Senior Software Engineer (Python, DBT, ETL)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.4</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,40 +741,320 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291bce23f034d334</t>
+          <t>https://www.indeed.com/viewjob?jk=e11531ce39be3674</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Senior Software Engineer (Python, DBT, ETL)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RevSpring, Inc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c82f7de5f84e4fb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sr Java Developer with E-Trading exp must</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NSV IT SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b93bfb157e46dad0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Copart, Inc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75d032017053c612</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sr. Database Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=669e23632e4f9ad7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior MuleSoft Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Green Irony</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior MuleSoft Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Green Irony</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apex, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer III- Python, Databricks</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=291bce23f034d334</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Oracle, Tableau, Jenkins, Maven, Jenkins, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e76b66fdbbfac5e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Backend Software Engineer Intern (TikTok- PGC-Digital Content Center) - 2027 Summer</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>San Jose, CA, US USA</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D18" t="n">
         <v>10.4</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>AWS, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=df7f3bd6cb74fbdd</t>
         </is>

--- a/results/job_matches_2026-08-03.xlsx
+++ b/results/job_matches_2026-08-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,60 +783,60 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Java Developer with E-Trading exp must</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NSV IT SOLUTIONS</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b93bfb157e46dad0</t>
+          <t>https://www.indeed.com/viewjob?jk=99ee79c55904224f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Sr Java Developer with E-Trading exp must</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>NSV IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d032017053c612</t>
+          <t>https://www.indeed.com/viewjob?jk=b93bfb157e46dad0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Database Reliability Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>TritonExec</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Avenel, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669e23632e4f9ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=75d032017053c612</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Sr. Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=669e23632e4f9ad7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291bce23f034d334</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Oracle, Tableau, Jenkins, Maven, Jenkins, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e76b66fdbbfac5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Backend Software Engineer Intern (TikTok- PGC-Digital Content Center) - 2027 Summer</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,15 +1046,85 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=291bce23f034d334</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Oracle, Tableau, Jenkins, Maven, Jenkins, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e76b66fdbbfac5e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Backend Software Engineer Intern (TikTok- PGC-Digital Content Center) - 2027 Summer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=df7f3bd6cb74fbdd</t>
         </is>

--- a/results/job_matches_2026-08-03.xlsx
+++ b/results/job_matches_2026-08-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,52 +818,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Java Developer with E-Trading exp must</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NSV IT SOLUTIONS</t>
+          <t>TritonExec</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Avenel, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b93bfb157e46dad0</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TritonExec</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avenel, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,77 +871,77 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
+          <t>https://www.indeed.com/viewjob?jk=75d032017053c612</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Carlstadt, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d032017053c612</t>
+          <t>https://www.indeed.com/viewjob?jk=aaaec41fa04316f0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Database Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra, Data Modeling</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,137 +951,137 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669e23632e4f9ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Data Engineer With GenAI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Broadmind INC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Sr. Solutions Architect - Financial Services (Strategic Banking)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291bce23f034d334</t>
+          <t>https://www.indeed.com/viewjob?jk=bb00340cb94b420d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Oracle, Tableau, Jenkins, Maven, Jenkins, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,40 +1091,250 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e76b66fdbbfac5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Sr. Database Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=669e23632e4f9ad7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Process Automation Senior Developer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e8c88eeba29b437</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior MuleSoft Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Green Irony</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior MuleSoft Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Green Irony</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apex, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer III- Python, Databricks</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=291bce23f034d334</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Backend Software Engineer Intern (TikTok- PGC-Digital Content Center) - 2027 Summer</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>San Jose, CA, US USA</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D26" t="n">
         <v>10.4</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>AWS, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=df7f3bd6cb74fbdd</t>
         </is>

--- a/results/job_matches_2026-08-03.xlsx
+++ b/results/job_matches_2026-08-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Site Reliability Engineer (SRE) with Data Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TritonExec</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avenel, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d0e50cf413f04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>TritonExec</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Avenel, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,59 +871,59 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d032017053c612</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dev Ops Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Carlstadt, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaaec41fa04316f0</t>
+          <t>https://www.indeed.com/viewjob?jk=75d032017053c612</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,15 +933,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Carlstadt, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=aaaec41fa04316f0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer With GenAI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Broadmind INC</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Financial Services (Strategic Banking)</t>
+          <t>Data Engineer With GenAI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Broadmind INC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb00340cb94b420d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Senior Specialty Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1ab076bac74b1c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Database Reliability Engineer</t>
+          <t>Sr. Solutions Architect - Financial Services (Strategic Banking)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669e23632e4f9ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=bb00340cb94b420d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Process Automation Senior Developer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e8c88eeba29b437</t>
+          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Sr. Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=669e23632e4f9ad7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Process Automation Senior Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e8c88eeba29b437</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,42 +1301,77 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291bce23f034d334</t>
+          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Backend Software Engineer Intern (TikTok- PGC-Digital Content Center) - 2027 Summer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Associate Data Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kimball Midwest</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>10.4</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df7f3bd6cb74fbdd</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball, ETL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39d5e9bfca8324e5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-03.xlsx
+++ b/results/job_matches_2026-08-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>DevOps Engineer - Westlake, TX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TritonExec</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avenel, NJ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
+          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>DevOps Engineer - Jersey City, NJ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d032017053c612</t>
+          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dev Ops Engineer</t>
+          <t>DevOps Engineer - Merrimack, NH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Carlstadt, NJ, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaaec41fa04316f0</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
         </is>
       </c>
     </row>
@@ -998,20 +998,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>Allied Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer With GenAI</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Broadmind INC</t>
+          <t>TritonExec</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Avenel, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, NoSQL, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1ab076bac74b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=75d032017053c612</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Financial Services (Strategic Banking)</t>
+          <t>Software Engineer III - AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb00340cb94b420d</t>
+          <t>https://www.indeed.com/viewjob?jk=9be9abf2ba504bc8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Carlstadt, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=aaaec41fa04316f0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Database Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra, Data Modeling</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669e23632e4f9ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Process Automation Senior Developer</t>
+          <t>Associate Cloud Engineer -</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,102 +1231,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e8c88eeba29b437</t>
+          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Operations Research Specialist - QuantumBlack Labs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Operations Research Specialist - Critical Industries</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,40 +1336,740 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
+          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The Hershey Company</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hershey, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21c0e185b38b0100</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GRP Solutions</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Engineer With GenAI</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Broadmind INC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Cloud-Native Architect</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71f63292ca49d08f</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Specialty Software Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, NoSQL, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e1ab076bac74b1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Architect - Financial Services (Strategic Banking)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb00340cb94b420d</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Machine Learning Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>IPolarity LLC</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Whippany, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Engineer III - Software</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PODS</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Clearwater, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sr. Database Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=669e23632e4f9ad7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Backend Developer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Progressive Technology Solutions</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Process Automation Senior Developer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e8c88eeba29b437</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior MuleSoft Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Green Irony</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior MuleSoft Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Green Irony</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Apex, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Engineer III - Software</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PODS</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Clearwater, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Cybersecurity Data Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sr. Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Microsoft Azure Specialist</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=797c8733d467365d</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Developer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>Associate Data Engineer</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Kimball Midwest</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Columbus, OH, US USA</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D47" t="n">
         <v>10.4</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=39d5e9bfca8324e5</t>
         </is>

--- a/results/job_matches_2026-08-03.xlsx
+++ b/results/job_matches_2026-08-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,35 +678,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, DBT, ETL)</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>FalconSmartIT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1c4c6a8a8c46e</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c0d190ff6325ff</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e11531ce39be3674</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd1c4c6a8a8c46e</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82f7de5f84e4fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=e11531ce39be3674</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Senior Software Engineer (Python, DBT, ETL)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>arrivia</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
+          <t>Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ee79c55904224f</t>
+          <t>https://www.indeed.com/viewjob?jk=c82f7de5f84e4fb8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) with Data Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d0e50cf413f04</t>
+          <t>https://www.indeed.com/viewjob?jk=b8353987748b8d8c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Westlake, TX</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=99ee79c55904224f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Jersey City, NJ</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Merrimack, NH</t>
+          <t>Site Reliability Engineer (SRE) with Data Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d0e50cf413f04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>DevOps Engineer - Westlake, TX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
+          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer - Jersey City, NJ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Allied Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
+          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>DevOps Engineer - Merrimack, NH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TritonExec</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avenel, NJ, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Sr. Analyst, Data Modeling</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>Redshift, IAM, RDS, Databricks, BigQuery, HBase, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d032017053c612</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b4125cc7e6462</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, MLOps, CI/CD</t>
+          <t>Azure, Databricks, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be9abf2ba504bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=cf971bdf2ccdd305</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dev Ops Engineer</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Carlstadt, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaaec41fa04316f0</t>
+          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
         </is>
       </c>
     </row>
@@ -1173,20 +1173,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Allied Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
+          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Associate Cloud Engineer -</t>
+          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - QuantumBlack Labs</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>TritonExec</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Avenel, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - Critical Industries</t>
+          <t>Enterprise Architect - Multi Cloud</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=c5698f847899a449</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>DevOps Engineer III - REMOTE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c0e185b38b0100</t>
+          <t>https://www.indeed.com/viewjob?jk=d15fab4f2cde8bce</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
+          <t>https://www.indeed.com/viewjob?jk=75d032017053c612</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
+          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer With GenAI</t>
+          <t>Software Engineer III - AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Broadmind INC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=9be9abf2ba504bc8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carlstadt, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f63292ca49d08f</t>
+          <t>https://www.indeed.com/viewjob?jk=aaaec41fa04316f0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, NoSQL, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1ab076bac74b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Financial Services (Strategic Banking)</t>
+          <t>Associate Cloud Engineer -</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb00340cb94b420d</t>
+          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
+          <t>https://www.indeed.com/viewjob?jk=6707e3755a595393</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Database Reliability Engineer</t>
+          <t>Operations Research Specialist - QuantumBlack Labs</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669e23632e4f9ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Operations Research Specialist - Critical Industries</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
+          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Process Automation Senior Developer</t>
+          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e8c88eeba29b437</t>
+          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=21c0e185b38b0100</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
+          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer With GenAI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Broadmind INC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
+          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer</t>
+          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
+          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
+          <t>https://www.indeed.com/viewjob?jk=71f63292ca49d08f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Senior Specialty Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=797c8733d467365d</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1ab076bac74b1c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,40 +2036,810 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+          <t>https://www.indeed.com/viewjob?jk=eadd2826582327ff</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>Sr. Solutions Architect - Financial Services (Strategic Banking)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb00340cb94b420d</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Machine Learning Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>IPolarity LLC</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Whippany, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Engineer III - Software</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PODS</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Clearwater, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AI Agentic Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Confiz</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Engineer III - Software</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PODS</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Clearwater, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Backend Developer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Progressive Technology Solutions</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Process Automation Senior Developer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e8c88eeba29b437</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior MuleSoft Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Green Irony</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior MuleSoft Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Green Irony</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Apex, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Technology Internship Program - Summer 2027</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Cybersecurity Data Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Healthcare Data Scientist</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Cherokee Federal</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Sr. Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=610c3a1bbde2965d</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Developer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Solutions Architect - AI Natives Business, Strategic</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42ea35aceaecf2e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Digital Native Business, Named Accounts</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9d04b632592cdc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Microsoft Azure Specialist</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=797c8733d467365d</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>Associate Data Engineer</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Kimball Midwest</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Columbus, OH, US USA</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D69" t="n">
         <v>10.4</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=39d5e9bfca8324e5</t>
         </is>

--- a/results/job_matches_2026-08-03.xlsx
+++ b/results/job_matches_2026-08-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,60 +818,60 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>BTI Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8353987748b8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf03b9bdd21cf939</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Azure Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>arrivia</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ee79c55904224f</t>
+          <t>https://www.indeed.com/viewjob?jk=55b8b8abc753de7f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
+          <t>https://www.indeed.com/viewjob?jk=b8353987748b8d8c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) with Data Platform</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d0e50cf413f04</t>
+          <t>https://www.indeed.com/viewjob?jk=99ee79c55904224f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Westlake, TX</t>
+          <t>Full-Stack Developer - Integrations</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Jersey City, NJ</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Merrimack, NH</t>
+          <t>Site Reliability Engineer (SRE) with Data Platform</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d0e50cf413f04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data Modeling</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Databricks, BigQuery, HBase, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b4125cc7e6462</t>
+          <t>https://www.indeed.com/viewjob?jk=5104197d6abcdbd0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer - Westlake, TX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf971bdf2ccdd305</t>
+          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>DevOps Engineer - Jersey City, NJ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
+          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer - Merrimack, NH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Allied Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
+          <t>Sr. Analyst, Data Modeling</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>Redshift, IAM, RDS, Databricks, BigQuery, HBase, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b4125cc7e6462</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=cf971bdf2ccdd305</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TritonExec</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avenel, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
+          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Multi Cloud</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Allied Solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5698f847899a449</t>
+          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer III - REMOTE</t>
+          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15fab4f2cde8bce</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d032017053c612</t>
+          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>TritonExec</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Avenel, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Engineer</t>
+          <t>Enterprise Architect - Multi Cloud</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be9abf2ba504bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=c5698f847899a449</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dev Ops Engineer</t>
+          <t>Senior Solutions Architect - Airflow - East Coast</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Carlstadt, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaaec41fa04316f0</t>
+          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Solutions Architect - Airflow - West Coast</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
+          <t>https://www.indeed.com/viewjob?jk=310b444ca9a8968f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate Cloud Engineer -</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
+          <t>https://www.indeed.com/viewjob?jk=75d032017053c612</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>DevOps Engineer III - REMOTE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6707e3755a595393</t>
+          <t>https://www.indeed.com/viewjob?jk=d15fab4f2cde8bce</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - QuantumBlack Labs</t>
+          <t>Data Intelligence Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=1f523df076b59e1d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - Critical Industries</t>
+          <t>Software Engineer III - AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=9be9abf2ba504bc8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Associate Cloud Engineer -</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c0e185b38b0100</t>
+          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
+          <t>https://www.indeed.com/viewjob?jk=6707e3755a595393</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer With GenAI</t>
+          <t>Operations Research Specialist - QuantumBlack Labs</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Broadmind INC</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
+          <t>Operations Research Specialist - Critical Industries</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f63292ca49d08f</t>
+          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, NoSQL, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1ab076bac74b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=21c0e185b38b0100</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd2826582327ff</t>
+          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Financial Services (Strategic Banking)</t>
+          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb00340cb94b420d</t>
+          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Data Engineer With GenAI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Broadmind INC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
+          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Agentic Solutions Engineer</t>
+          <t>Generative AI / Enterprise Data Senior Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>General Dynamics Land Systems</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
+          <t>https://www.indeed.com/viewjob?jk=eadd2826582327ff</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
+          <t>https://www.indeed.com/viewjob?jk=71f63292ca49d08f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Senior Specialty Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1ab076bac74b1c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Sr. Solutions Architect - Financial Services (Strategic Banking)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
+          <t>https://www.indeed.com/viewjob?jk=bb00340cb94b420d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Consumers Energy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
+          <t>https://www.indeed.com/viewjob?jk=100d36e57f68f74b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Process Automation Senior Developer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,59 +2386,59 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e8c88eeba29b437</t>
+          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>AI Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Technology Internship Program - Summer 2027</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
+          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
+          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Healthcare Data Scientist</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cherokee Federal</t>
+          <t>Progressive Technology Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
+          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer</t>
+          <t>Process Automation Senior Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,102 +2596,102 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2e8c88eeba29b437</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=610c3a1bbde2965d</t>
+          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI Natives Business, Strategic</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ea35aceaecf2e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Solutions Architect - Digital Native Business, Named Accounts</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9d04b632592cdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Data Scientist / AI Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LG Electronics</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=797c8733d467365d</t>
+          <t>https://www.indeed.com/viewjob?jk=2503df5e5b9aa571</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Technology Internship Program - Summer 2027</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,15 +2831,435 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Cybersecurity Data Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Healthcare Data Scientist</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Cherokee Federal</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sr. Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Solutions Architect - AI Natives Business, Strategic</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42ea35aceaecf2e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=610c3a1bbde2965d</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Digital Native Business, Named Accounts</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9d04b632592cdc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Microsoft Azure Specialist</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=797c8733d467365d</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Developer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Raritan, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Associate Data Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Kimball Midwest</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=39d5e9bfca8324e5</t>
         </is>

--- a/results/job_matches_2026-08-03.xlsx
+++ b/results/job_matches_2026-08-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Microsoft Power BI Technical Specialist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>26.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>Kinesis, Redshift, S3, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec018f4b793bb53</t>
+          <t>https://www.indeed.com/viewjob?jk=c4eb0dda56977ab6</t>
         </is>
       </c>
     </row>
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5406e0a898c0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec018f4b793bb53</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51afe960d8622afb</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5406e0a898c0b3</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bdbda24615b096</t>
+          <t>https://www.indeed.com/viewjob?jk=51afe960d8622afb</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a792597231fd045</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bdbda24615b096</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b79f56ab220c49</t>
+          <t>https://www.indeed.com/viewjob?jk=8a792597231fd045</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FalconSmartIT</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c0d190ff6325ff</t>
+          <t>https://www.indeed.com/viewjob?jk=49b79f56ab220c49</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, DBT, ETL)</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>FalconSmartIT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1c4c6a8a8c46e</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c0d190ff6325ff</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e11531ce39be3674</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd1c4c6a8a8c46e</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,42 +811,42 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82f7de5f84e4fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=e11531ce39be3674</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Senior Software Engineer (Python, DBT, ETL)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf03b9bdd21cf939</t>
+          <t>https://www.indeed.com/viewjob?jk=c82f7de5f84e4fb8</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full-Stack Developer - Integrations</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8b2fd3d76ce63e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Developer - Integrations</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
+          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) with Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d0e50cf413f04</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Site Reliability Engineer (SRE) with Data Platform</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5104197d6abcdbd0</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d0e50cf413f04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Westlake, TX</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=5104197d6abcdbd0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Jersey City, NJ</t>
+          <t>DevOps Engineer - Westlake, TX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Merrimack, NH</t>
+          <t>DevOps Engineer - Jersey City, NJ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
+          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data Modeling</t>
+          <t>DevOps Engineer - Merrimack, NH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Databricks, BigQuery, HBase, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b4125cc7e6462</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Analyst, Data Modeling</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>Redshift, IAM, RDS, Databricks, BigQuery, HBase, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf971bdf2ccdd305</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b4125cc7e6462</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>Azure, Databricks, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
+          <t>https://www.indeed.com/viewjob?jk=cf971bdf2ccdd305</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Allied Solutions</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
+          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Allied Solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, BigQuery, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
+          <t>https://www.indeed.com/viewjob?jk=c1386463efa42576</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TritonExec</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avenel, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
+          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Multi Cloud</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TritonExec</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Avenel, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5698f847899a449</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow - East Coast</t>
+          <t>Enterprise Architect - Multi Cloud</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
+          <t>https://www.indeed.com/viewjob?jk=c5698f847899a449</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow - West Coast</t>
+          <t>Senior Solutions Architect - Airflow - East Coast</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310b444ca9a8968f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>DevOps Engineer III - REMOTE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d032017053c612</t>
+          <t>https://www.indeed.com/viewjob?jk=d15fab4f2cde8bce</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer III - REMOTE</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15fab4f2cde8bce</t>
+          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Data Intelligence Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
+          <t>https://www.indeed.com/viewjob?jk=1f523df076b59e1d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Intelligence Analyst</t>
+          <t>Software Engineer III - AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f523df076b59e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=9be9abf2ba504bc8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be9abf2ba504bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Cloud Engineer -</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt</t>
+          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd37781709951727</t>
+          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Associate Cloud Engineer -</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
+          <t>https://www.indeed.com/viewjob?jk=6707e3755a595393</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>Operations Research Specialist - QuantumBlack Labs</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6707e3755a595393</t>
+          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Operations Research Specialist - Critical Industries</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - QuantumBlack Labs</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7274d25e3e7cbd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - Critical Industries</t>
+          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Dask, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=21c0e185b38b0100</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c0e185b38b0100</t>
+          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933b131b771651ee</t>
+          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fa19c8aafe8e13</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer With GenAI</t>
+          <t>Sr. DevOps / Cloud Engineer, Billing Infrastructure</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Broadmind INC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Google Cloud Platform, Scala, Snowflake, MySQL, Jenkins, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=215a3df996bed07f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
+          <t>Data Engineer With GenAI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Broadmind INC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Generative AI / Enterprise Data Senior Architect</t>
+          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>General Dynamics Land Systems</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
+          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd2826582327ff</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0f689bfea9b199</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f63292ca49d08f</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer</t>
+          <t>Generative AI / Enterprise Data Senior Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>General Dynamics Land Systems</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, NoSQL, GitHub Actions</t>
+          <t>RDS, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1ab076bac74b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Financial Services (Strategic Banking)</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb00340cb94b420d</t>
+          <t>https://www.indeed.com/viewjob?jk=eadd2826582327ff</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Consumers Energy</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100d36e57f68f74b</t>
+          <t>https://www.indeed.com/viewjob?jk=71f63292ca49d08f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior Specialty Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1ab076bac74b1c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Sr. Solutions Architect - Financial Services (Strategic Banking)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=bb00340cb94b420d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Agentic Solutions Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Consumers Energy</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=100d36e57f68f74b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
+          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
+          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>AI Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
+          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Process Automation Senior Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e8c88eeba29b437</t>
+          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>Progressive Technology Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Azure Cosmos DB</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
+          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Process Automation Senior Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
+          <t>https://www.indeed.com/viewjob?jk=2e8c88eeba29b437</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
+          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Scientist / AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, Cassandra, Maven, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2503df5e5b9aa571</t>
+          <t>https://www.indeed.com/viewjob?jk=9929d5929d1dfc52</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Technology Internship Program - Summer 2027</t>
+          <t>Data Scientist / AI Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>LG Electronics</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Power BI, Tableau, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
+          <t>https://www.indeed.com/viewjob?jk=2503df5e5b9aa571</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer</t>
+          <t>Technology Internship Program - Summer 2027</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff7cf8968808f78</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Healthcare Data Scientist</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cherokee Federal</t>
+          <t>Sporttrade</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0f5d76f45500</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
+          <t>Healthcare Data Scientist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cherokee Federal</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
+          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI Natives Business, Strategic</t>
+          <t>Sr. Backend Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ea35aceaecf2e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
+          <t>Senior IT Systems Engineer-ORCA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Sound Transit</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=610c3a1bbde2965d</t>
+          <t>https://www.indeed.com/viewjob?jk=4595ccfdbf2b393d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Solutions Architect - Digital Native Business, Named Accounts</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9d04b632592cdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=797c8733d467365d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+          <t>https://www.indeed.com/viewjob?jk=610c3a1bbde2965d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect - AI Natives Business, Strategic</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, MLOps, CodeBuild</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
+          <t>https://www.indeed.com/viewjob?jk=42ea35aceaecf2e7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Solutions Architect - Digital Native Business, Named Accounts</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,15 +3251,120 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9d04b632592cdc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Microsoft Azure Specialist</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=797c8733d467365d</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Developer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Associate Data Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Kimball Midwest</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=39d5e9bfca8324e5</t>
         </is>
